--- a/data/trans_dic/P1002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,46</t>
+          <t>0,71; 3,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,52</t>
+          <t>1,02; 3,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,05</t>
+          <t>1,03; 4,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,74</t>
+          <t>1,6; 4,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,66</t>
+          <t>2,79; 6,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,06</t>
+          <t>1,19; 4,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 10,98</t>
+          <t>2,65; 10,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,34</t>
+          <t>1,36; 3,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,57</t>
+          <t>2,18; 4,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,43</t>
+          <t>1,39; 3,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,58</t>
+          <t>1,49; 5,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,98</t>
+          <t>1,58; 4,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,5</t>
+          <t>1,54; 4,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,8</t>
+          <t>2,29; 5,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,06</t>
+          <t>1,19; 6,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,22</t>
+          <t>4,24; 8,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,1</t>
+          <t>3,34; 7,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,72</t>
+          <t>2,47; 5,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,18</t>
+          <t>2,85; 8,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,43</t>
+          <t>3,1; 5,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,08</t>
+          <t>2,79; 4,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,05</t>
+          <t>2,78; 5,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,35</t>
+          <t>2,82; 6,4</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,97</t>
+          <t>2,6; 5,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,38</t>
+          <t>2,97; 6,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,05</t>
+          <t>2,16; 5,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,77</t>
+          <t>3,51; 7,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,09</t>
+          <t>3,72; 7,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 14,06</t>
+          <t>8,85; 13,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,06</t>
+          <t>4,25; 7,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,2</t>
+          <t>3,96; 7,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,95</t>
+          <t>3,62; 5,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,57</t>
+          <t>6,45; 9,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,02</t>
+          <t>3,63; 5,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,71</t>
+          <t>4,16; 6,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,84</t>
+          <t>3,06; 6,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,18</t>
+          <t>4,59; 9,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,65</t>
+          <t>4,36; 8,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,36</t>
+          <t>1,89; 7,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,66</t>
+          <t>7,27; 12,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 15,87</t>
+          <t>10,38; 16,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,23</t>
+          <t>7,66; 12,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,3</t>
+          <t>6,59; 11,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,14</t>
+          <t>5,72; 9,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,86</t>
+          <t>7,99; 11,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,53</t>
+          <t>6,44; 9,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,35</t>
+          <t>4,07; 8,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,41</t>
+          <t>5,07; 10,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 12,37</t>
+          <t>6,5; 11,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,26</t>
+          <t>3,81; 8,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,21</t>
+          <t>5,91; 10,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 13,13</t>
+          <t>7,16; 13,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 23,63</t>
+          <t>16,09; 23,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,85</t>
+          <t>12,7; 19,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,55</t>
+          <t>10,52; 14,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 10,94</t>
+          <t>6,71; 10,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,2; 17,1</t>
+          <t>12,3; 17,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 13,33</t>
+          <t>9,0; 13,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,59</t>
+          <t>8,66; 11,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 14,38</t>
+          <t>7,55; 14,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 16,98</t>
+          <t>9,14; 17,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,43</t>
+          <t>6,15; 12,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,78</t>
+          <t>5,6; 9,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 18,21</t>
+          <t>10,88; 18,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,38; 26,12</t>
+          <t>17,63; 25,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,86; 21,89</t>
+          <t>14,34; 22,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 14,7</t>
+          <t>3,79; 14,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,94; 15,17</t>
+          <t>10,19; 15,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,41; 20,33</t>
+          <t>14,27; 20,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,18</t>
+          <t>11,27; 16,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 11,38</t>
+          <t>4,07; 11,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,41; 21,34</t>
+          <t>11,34; 21,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,17; 27,83</t>
+          <t>16,36; 27,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,27; 15,8</t>
+          <t>8,62; 15,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,12; 14,28</t>
+          <t>8,28; 14,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,3; 23,88</t>
+          <t>14,17; 23,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,9; 36,96</t>
+          <t>26,89; 36,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,56; 29,61</t>
+          <t>19,74; 29,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,79; 28,13</t>
+          <t>21,67; 27,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,39; 21,34</t>
+          <t>14,2; 21,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,17; 31,54</t>
+          <t>24,48; 31,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,25; 23,33</t>
+          <t>16,39; 23,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,29</t>
+          <t>17,0; 21,38</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,02</t>
+          <t>4,48; 6,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,75</t>
+          <t>5,85; 7,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,17</t>
+          <t>4,57; 6,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,32</t>
+          <t>4,17; 6,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,52</t>
+          <t>7,53; 9,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,88; 15,19</t>
+          <t>12,89; 15,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,62; 11,71</t>
+          <t>9,66; 11,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,08</t>
+          <t>8,03; 11,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,53</t>
+          <t>6,26; 7,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,17</t>
+          <t>9,69; 11,13</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,7</t>
+          <t>7,39; 8,75</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,55</t>
+          <t>6,75; 8,64</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3807; 17083</t>
+          <t>3502; 16593</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4550; 15984</t>
+          <t>4620; 16526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4267; 16990</t>
+          <t>4304; 17025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 16846</t>
+          <t>0; 19619</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7533; 22182</t>
+          <t>7500; 21705</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11709; 28642</t>
+          <t>11990; 29711</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4024; 16085</t>
+          <t>4720; 16653</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9046; 34388</t>
+          <t>8313; 33341</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13809; 32111</t>
+          <t>13105; 33554</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18815; 40372</t>
+          <t>19256; 40092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11239; 27939</t>
+          <t>11343; 28193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11262; 39813</t>
+          <t>10595; 37690</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11122; 29270</t>
+          <t>11584; 29566</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11101; 30937</t>
+          <t>10573; 28664</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13644; 34220</t>
+          <t>13550; 33697</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5525; 25675</t>
+          <t>5026; 25844</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26268; 51390</t>
+          <t>26495; 51995</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21387; 43310</t>
+          <t>20400; 43588</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14159; 32256</t>
+          <t>13928; 32040</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14111; 41835</t>
+          <t>14578; 41574</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41500; 73948</t>
+          <t>42211; 73885</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37319; 65877</t>
+          <t>36200; 64597</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32526; 58239</t>
+          <t>32080; 59019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26849; 59359</t>
+          <t>26368; 59883</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15791; 38122</t>
+          <t>16627; 38160</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20448; 43428</t>
+          <t>20207; 44117</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14074; 33817</t>
+          <t>14431; 33508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18871; 41675</t>
+          <t>18852; 41554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25227; 48921</t>
+          <t>25654; 48669</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65192; 99956</t>
+          <t>62937; 96991</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28630; 53327</t>
+          <t>28106; 51874</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21573; 39075</t>
+          <t>21493; 38736</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47338; 79090</t>
+          <t>48025; 78392</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91113; 133261</t>
+          <t>89752; 131079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48347; 80161</t>
+          <t>48256; 78908</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44255; 72381</t>
+          <t>44916; 73447</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15570; 35528</t>
+          <t>15889; 34851</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28290; 56301</t>
+          <t>28140; 57284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29848; 55910</t>
+          <t>28159; 54219</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17689; 65311</t>
+          <t>16787; 64930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38512; 65281</t>
+          <t>37494; 64888</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64394; 97804</t>
+          <t>63975; 98862</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47977; 79377</t>
+          <t>49725; 78759</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48539; 80580</t>
+          <t>46983; 79099</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59212; 94528</t>
+          <t>59148; 93130</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99765; 145888</t>
+          <t>98284; 142267</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83753; 123395</t>
+          <t>83436; 124020</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58819; 133625</t>
+          <t>65104; 134468</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19679; 40276</t>
+          <t>19600; 41297</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28169; 53118</t>
+          <t>27900; 51489</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18449; 39460</t>
+          <t>18187; 39257</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33720; 57307</t>
+          <t>33195; 57205</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29119; 53026</t>
+          <t>28916; 53448</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72596; 105551</t>
+          <t>71895; 104517</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64306; 98624</t>
+          <t>63107; 97298</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>56922; 79667</t>
+          <t>57581; 80678</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54597; 86498</t>
+          <t>53036; 85758</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106856; 149854</t>
+          <t>107780; 148911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87294; 129971</t>
+          <t>87740; 128802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94601; 128524</t>
+          <t>95991; 129856</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21519; 42076</t>
+          <t>22087; 41974</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28772; 52591</t>
+          <t>28329; 54606</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20165; 41541</t>
+          <t>20572; 41482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19602; 35952</t>
+          <t>20572; 36422</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38210; 62445</t>
+          <t>37307; 61972</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61360; 92215</t>
+          <t>62231; 91189</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52353; 82677</t>
+          <t>54176; 83349</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22801; 89450</t>
+          <t>23049; 89538</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63162; 96392</t>
+          <t>64754; 97354</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95508; 134734</t>
+          <t>94603; 135013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78781; 115213</t>
+          <t>80220; 118444</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40698; 111064</t>
+          <t>39704; 111175</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23944; 44783</t>
+          <t>23804; 45063</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40405; 69523</t>
+          <t>40880; 68418</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21242; 40606</t>
+          <t>22166; 40859</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22903; 40275</t>
+          <t>23350; 39817</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47733; 79738</t>
+          <t>47324; 77478</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>104642; 143777</t>
+          <t>104588; 143311</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78270; 118493</t>
+          <t>78999; 118284</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>92448; 119368</t>
+          <t>91937; 116995</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78230; 116059</t>
+          <t>77231; 115509</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154410; 201479</t>
+          <t>156404; 202957</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>106815; 153333</t>
+          <t>107679; 153497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>119911; 150416</t>
+          <t>120099; 151039</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>146413; 197135</t>
+          <t>146756; 198797</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202429; 265576</t>
+          <t>200223; 262762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>157335; 209501</t>
+          <t>155036; 210026</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>143983; 218652</t>
+          <t>144095; 218060</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>253234; 321680</t>
+          <t>254321; 320284</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>458056; 540116</t>
+          <t>458486; 543955</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>341007; 415129</t>
+          <t>342362; 420308</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>297598; 405500</t>
+          <t>293952; 409591</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>416591; 501248</t>
+          <t>416760; 498152</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>674567; 780114</t>
+          <t>676277; 777108</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>512014; 603749</t>
+          <t>512495; 607279</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>477718; 608844</t>
+          <t>480796; 614848</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,36</t>
+          <t>0,65; 3,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,64</t>
+          <t>1,03; 3,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,06</t>
+          <t>1,03; 3,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,64</t>
+          <t>1,58; 4,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,91</t>
+          <t>2,89; 6,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,21</t>
+          <t>1,05; 4,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,65</t>
+          <t>3,0; 10,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,49</t>
+          <t>1,45; 3,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,53</t>
+          <t>2,17; 4,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,46</t>
+          <t>1,35; 3,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,28</t>
+          <t>1,72; 5,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,02</t>
+          <t>1,63; 4,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,17</t>
+          <t>1,57; 4,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,71</t>
+          <t>2,38; 5,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,1</t>
+          <t>1,21; 6,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,31</t>
+          <t>4,5; 8,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,14</t>
+          <t>3,44; 7,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,69</t>
+          <t>2,51; 5,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,13</t>
+          <t>3,8; 9,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,43</t>
+          <t>3,17; 5,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,98</t>
+          <t>2,81; 5,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,11</t>
+          <t>2,78; 5,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,4</t>
+          <t>2,95; 6,25</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,97</t>
+          <t>2,71; 6,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,48</t>
+          <t>3,13; 6,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,01</t>
+          <t>2,2; 5,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,75</t>
+          <t>3,27; 7,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,06</t>
+          <t>3,55; 7,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 13,64</t>
+          <t>8,78; 13,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,84</t>
+          <t>4,32; 8,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,14</t>
+          <t>3,92; 7,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,9</t>
+          <t>3,53; 5,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,42</t>
+          <t>6,39; 9,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,93</t>
+          <t>3,58; 5,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,81</t>
+          <t>4,06; 6,37</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,71</t>
+          <t>3,02; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,34</t>
+          <t>4,64; 9,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,39</t>
+          <t>4,55; 8,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,31</t>
+          <t>4,42; 8,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 12,58</t>
+          <t>7,31; 12,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,04</t>
+          <t>10,23; 16,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,13</t>
+          <t>7,56; 12,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,1</t>
+          <t>6,69; 10,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,0</t>
+          <t>5,74; 8,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,57</t>
+          <t>8,14; 11,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,58</t>
+          <t>6,48; 9,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,4</t>
+          <t>6,03; 8,58</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,68</t>
+          <t>5,08; 9,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,99</t>
+          <t>6,69; 12,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,21</t>
+          <t>3,7; 8,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,19</t>
+          <t>5,48; 9,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,23</t>
+          <t>7,36; 13,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 23,4</t>
+          <t>15,86; 23,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,7; 19,58</t>
+          <t>12,76; 19,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,73</t>
+          <t>10,85; 15,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,85</t>
+          <t>6,92; 11,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,3; 17,0</t>
+          <t>12,39; 17,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,21</t>
+          <t>9,09; 13,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,71</t>
+          <t>8,7; 11,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,35</t>
+          <t>7,33; 14,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 17,63</t>
+          <t>8,83; 17,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 12,41</t>
+          <t>6,09; 12,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,91</t>
+          <t>5,64; 9,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 18,07</t>
+          <t>10,78; 17,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,63; 25,83</t>
+          <t>17,05; 25,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,34; 22,06</t>
+          <t>13,98; 22,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,72</t>
+          <t>11,99; 16,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,32</t>
+          <t>10,08; 15,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,27; 20,37</t>
+          <t>14,61; 20,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,27; 16,63</t>
+          <t>11,33; 16,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 11,39</t>
+          <t>9,4; 12,8</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,34; 21,47</t>
+          <t>11,98; 21,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,36; 27,38</t>
+          <t>16,66; 27,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 15,9</t>
+          <t>8,15; 15,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,11</t>
+          <t>8,62; 14,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,17; 23,2</t>
+          <t>14,12; 23,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,89; 36,84</t>
+          <t>26,85; 37,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,74; 29,56</t>
+          <t>19,74; 29,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,67; 27,57</t>
+          <t>22,22; 28,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,2; 21,24</t>
+          <t>14,71; 21,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,48; 31,77</t>
+          <t>24,41; 31,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,39; 23,36</t>
+          <t>16,58; 23,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,0; 21,38</t>
+          <t>17,61; 22,11</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,53; 6,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,67</t>
+          <t>5,94; 7,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,19</t>
+          <t>4,66; 6,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,3</t>
+          <t>5,0; 6,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,48</t>
+          <t>7,59; 9,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,89; 15,3</t>
+          <t>12,89; 15,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,86</t>
+          <t>9,53; 11,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,19</t>
+          <t>9,98; 11,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,48</t>
+          <t>6,28; 7,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,69; 11,13</t>
+          <t>9,71; 11,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,75</t>
+          <t>7,42; 8,75</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,64</t>
+          <t>7,72; 8,9</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>26293</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3502; 16593</t>
+          <t>3233; 16118</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4620; 16526</t>
+          <t>4671; 15861</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4304; 17025</t>
+          <t>4330; 16747</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 19619</t>
+          <t>0; 16006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7500; 21705</t>
+          <t>7393; 22133</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11990; 29711</t>
+          <t>12440; 29627</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4720; 16653</t>
+          <t>4137; 15943</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8313; 33341</t>
+          <t>10868; 39453</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13105; 33554</t>
+          <t>13944; 34592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19256; 40092</t>
+          <t>19169; 39652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11343; 28193</t>
+          <t>11035; 28280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10595; 37690</t>
+          <t>13246; 44010</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39605</t>
+          <t>43422</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11584; 29566</t>
+          <t>11973; 29487</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10573; 28664</t>
+          <t>10781; 28580</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13550; 33697</t>
+          <t>14071; 33636</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5026; 25844</t>
+          <t>5757; 29510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26495; 51995</t>
+          <t>28153; 51503</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20400; 43588</t>
+          <t>20995; 43451</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13928; 32040</t>
+          <t>14141; 32037</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14578; 41574</t>
+          <t>19032; 45242</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42211; 73885</t>
+          <t>43108; 75090</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36200; 64597</t>
+          <t>36500; 66319</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32080; 59019</t>
+          <t>32122; 58501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26368; 59883</t>
+          <t>28818; 61126</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57718</t>
+          <t>63700</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16627; 38160</t>
+          <t>17290; 39535</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20207; 44117</t>
+          <t>21280; 44075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14431; 33508</t>
+          <t>14720; 34399</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18852; 41554</t>
+          <t>20330; 44209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25654; 48669</t>
+          <t>24485; 48434</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62937; 96991</t>
+          <t>62402; 98753</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28106; 51874</t>
+          <t>28593; 53000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21493; 38736</t>
+          <t>24393; 43670</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48025; 78392</t>
+          <t>46878; 77584</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89752; 131079</t>
+          <t>88962; 131521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48256; 78908</t>
+          <t>47672; 77705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44916; 73447</t>
+          <t>50422; 79223</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41820</t>
+          <t>43366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>61505</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>103324</t>
+          <t>104617</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15889; 34851</t>
+          <t>15682; 35789</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28140; 57284</t>
+          <t>28483; 55842</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28159; 54219</t>
+          <t>29397; 54314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16787; 64930</t>
+          <t>31000; 59765</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37494; 64888</t>
+          <t>37679; 65698</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63975; 98862</t>
+          <t>63039; 98901</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49725; 78759</t>
+          <t>49067; 79938</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46983; 79099</t>
+          <t>49304; 73681</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59148; 93130</t>
+          <t>59370; 91281</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98284; 142267</t>
+          <t>100054; 143975</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83436; 124020</t>
+          <t>83882; 126096</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65104; 134468</t>
+          <t>86651; 123336</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43278</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68127</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>111405</t>
+          <t>122127</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19600; 41297</t>
+          <t>19638; 38629</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27900; 51489</t>
+          <t>28726; 52625</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18187; 39257</t>
+          <t>17694; 39852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33195; 57205</t>
+          <t>33415; 58170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28916; 53448</t>
+          <t>29716; 53354</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71895; 104517</t>
+          <t>70857; 106514</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63107; 97298</t>
+          <t>63404; 98147</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57581; 80678</t>
+          <t>66021; 92403</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53036; 85758</t>
+          <t>54710; 87303</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107780; 148911</t>
+          <t>108542; 151085</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87740; 128802</t>
+          <t>88573; 130290</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95991; 129856</t>
+          <t>105924; 139899</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>63430</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83885</t>
+          <t>93711</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22087; 41974</t>
+          <t>21448; 41525</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28329; 54606</t>
+          <t>27345; 52810</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20572; 41482</t>
+          <t>20364; 42166</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20572; 36422</t>
+          <t>22910; 40520</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37307; 61972</t>
+          <t>36985; 61319</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62231; 91189</t>
+          <t>60187; 90705</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54176; 83349</t>
+          <t>52806; 83510</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23049; 89538</t>
+          <t>52666; 73765</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64754; 97354</t>
+          <t>64052; 96050</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94603; 135013</t>
+          <t>96815; 135985</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80220; 118444</t>
+          <t>80677; 118061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39704; 111175</t>
+          <t>79480; 108264</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>35113</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>104572</t>
+          <t>116792</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>135034</t>
+          <t>151905</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23804; 45063</t>
+          <t>25136; 45572</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40880; 68418</t>
+          <t>41626; 69738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22166; 40859</t>
+          <t>20944; 40225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23350; 39817</t>
+          <t>26696; 45428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47324; 77478</t>
+          <t>47149; 77793</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>104588; 143311</t>
+          <t>104438; 143970</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78999; 118284</t>
+          <t>79006; 117248</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91937; 116995</t>
+          <t>102889; 130682</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>77231; 115509</t>
+          <t>79998; 114448</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>156404; 202957</t>
+          <t>155941; 203124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107679; 153497</t>
+          <t>108990; 153902</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>120099; 151039</t>
+          <t>136044; 170786</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187834</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>365157</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>552991</t>
+          <t>605775</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>146756; 198797</t>
+          <t>148464; 198912</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>200223; 262762</t>
+          <t>203429; 264601</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>155036; 210026</t>
+          <t>158177; 210644</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>144095; 218060</t>
+          <t>176467; 233558</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>254321; 320284</t>
+          <t>256407; 320052</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>458486; 543955</t>
+          <t>458375; 538013</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>342362; 420308</t>
+          <t>337941; 419802</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>293952; 409591</t>
+          <t>372575; 438334</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>416760; 498152</t>
+          <t>417963; 503940</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>676277; 777108</t>
+          <t>677517; 780673</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>512495; 607279</t>
+          <t>514784; 607076</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>480796; 614848</t>
+          <t>560588; 646768</t>
         </is>
       </c>
     </row>
